--- a/nexum_proyecto_final/resultados/resultados_modelo.xlsx
+++ b/nexum_proyecto_final/resultados/resultados_modelo.xlsx
@@ -23,6 +23,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riesgo_cambiario" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robustez" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Walk_forward" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidad_commodities" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2635,6 +2636,96 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Universo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cartera CAGR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cartera Sharpe</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Cartera máx. caída</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>P(3 objetivos) histórico</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Peso BL recalibrado commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5 ETF (vigente: GLD, USO, DBA, SLV, CPER)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.09993360885041302</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8497646103824529</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2047527980997259</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.95955</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06594458452445751</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3 ETF (original: GLD, USO, DBA)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.09736940269919536</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8336929616319234</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2042303300441655</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9477</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1014848299326839</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/nexum_proyecto_final/resultados/resultados_modelo.xlsx
+++ b/nexum_proyecto_final/resultados/resultados_modelo.xlsx
@@ -24,6 +24,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robustez" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Walk_forward" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidad_commodities" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contribucion_riesgo" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desempleo" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abanico_historico" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abanico_prospectivo" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2726,6 +2730,447 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Volatilidad propia</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Contribución al riesgo (%)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Contribución a la volatilidad (pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 (SPY)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1421053118531352</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4952643131930181</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.04909564306511672</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tesoro EE.UU. 10-20 años (TLH)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.09765102554900518</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.07393995594925706</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00732968152324841</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Corporativos largo plazo (VCLT)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1124289403205299</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1230897136322354</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.01220190610245014</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Momentum en commodities</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0611</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1698691890165765</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.02593952297280704</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.002571389715002553</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Momentum en acciones</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2376094730352182</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.119066258897765</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01180306028967858</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Low-Volatility</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1196037480284665</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1627002353549174</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01612850445471612</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Escenario de empleo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mercado</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>P(Educación)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>P(Villarrica)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>P(Herencia)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>P(3 objetivos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sin desempleo (base)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Histórico</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9813499999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.95955</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.95955</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sin desempleo (base)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Prospectivo</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4653</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4653</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5% anual, independiente del mercado; reempleo en ~2 años</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Histórico</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.97435</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9475</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9475</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5% anual, independiente del mercado; reempleo en ~2 años</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Prospectivo</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.66815</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4235</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5% normal y 25% si la cartera cayó &gt;10% en 12 meses; reempleo ~2 años</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Histórico</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.94385</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.94385</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5% normal y 25% si la cartera cayó &gt;10% en 12 meses; reempleo ~2 años</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Prospectivo</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.99995</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6542</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4141</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10% normal y 40% si la cartera cayó &gt;10%; reempleo ~2 años</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Histórico</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.96435</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9303</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9303</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10% normal y 40% si la cartera cayó &gt;10%; reempleo ~2 años</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Prospectivo</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.61055</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.37695</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Estrés: 6% anual y pérdida PERMANENTE (sin reempleo)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Histórico</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.99985</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.91245</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8655</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8655</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Estrés: 6% anual y pérdida PERMANENTE (sin reempleo)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Prospectivo</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9957</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5003</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3024</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2989,6 +3434,2138 @@
       </c>
       <c r="J7" t="n">
         <v>0.1196037480284665</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="B2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136454.1140377148</v>
+      </c>
+      <c r="B3" t="n">
+        <v>145546.7207558729</v>
+      </c>
+      <c r="C3" t="n">
+        <v>155716.3789750962</v>
+      </c>
+      <c r="D3" t="n">
+        <v>166313.6236591271</v>
+      </c>
+      <c r="E3" t="n">
+        <v>176050.4716673002</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>149671.6070711785</v>
+      </c>
+      <c r="B4" t="n">
+        <v>162679.5136214451</v>
+      </c>
+      <c r="C4" t="n">
+        <v>178615.3606225844</v>
+      </c>
+      <c r="D4" t="n">
+        <v>195244.6990507198</v>
+      </c>
+      <c r="E4" t="n">
+        <v>211621.6722000223</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>165345.9566355789</v>
+      </c>
+      <c r="B5" t="n">
+        <v>182118.4442534053</v>
+      </c>
+      <c r="C5" t="n">
+        <v>203316.6667978124</v>
+      </c>
+      <c r="D5" t="n">
+        <v>226051.6044996025</v>
+      </c>
+      <c r="E5" t="n">
+        <v>248357.9889515025</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>182419.22432318</v>
+      </c>
+      <c r="B6" t="n">
+        <v>203529.1119986085</v>
+      </c>
+      <c r="C6" t="n">
+        <v>229941.2008466994</v>
+      </c>
+      <c r="D6" t="n">
+        <v>258860.78612988</v>
+      </c>
+      <c r="E6" t="n">
+        <v>288271.5071260689</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>199689.5582582639</v>
+      </c>
+      <c r="B7" t="n">
+        <v>225812.4827342746</v>
+      </c>
+      <c r="C7" t="n">
+        <v>258541.4020198979</v>
+      </c>
+      <c r="D7" t="n">
+        <v>295487.0266135904</v>
+      </c>
+      <c r="E7" t="n">
+        <v>332315.7384546166</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>219410.2780986737</v>
+      </c>
+      <c r="B8" t="n">
+        <v>249979.7329628498</v>
+      </c>
+      <c r="C8" t="n">
+        <v>289547.1683824272</v>
+      </c>
+      <c r="D8" t="n">
+        <v>333678.9900654253</v>
+      </c>
+      <c r="E8" t="n">
+        <v>379620.5806192502</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>240419.1778380318</v>
+      </c>
+      <c r="B9" t="n">
+        <v>276066.6584250598</v>
+      </c>
+      <c r="C9" t="n">
+        <v>322860.2988122079</v>
+      </c>
+      <c r="D9" t="n">
+        <v>376379.5299027919</v>
+      </c>
+      <c r="E9" t="n">
+        <v>432771.8159162413</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>262517.5054301863</v>
+      </c>
+      <c r="B10" t="n">
+        <v>304571.807589428</v>
+      </c>
+      <c r="C10" t="n">
+        <v>358663.760112969</v>
+      </c>
+      <c r="D10" t="n">
+        <v>422156.8690035946</v>
+      </c>
+      <c r="E10" t="n">
+        <v>489374.5925807864</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>286193.0584790054</v>
+      </c>
+      <c r="B11" t="n">
+        <v>334213.4374750027</v>
+      </c>
+      <c r="C11" t="n">
+        <v>397298.5701881842</v>
+      </c>
+      <c r="D11" t="n">
+        <v>472304.1306883912</v>
+      </c>
+      <c r="E11" t="n">
+        <v>550908.4851284215</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>311851.514024121</v>
+      </c>
+      <c r="B12" t="n">
+        <v>366554.0147793446</v>
+      </c>
+      <c r="C12" t="n">
+        <v>438264.2073788026</v>
+      </c>
+      <c r="D12" t="n">
+        <v>524538.6908439768</v>
+      </c>
+      <c r="E12" t="n">
+        <v>618968.7294038442</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>339943.6078683768</v>
+      </c>
+      <c r="B13" t="n">
+        <v>402625.1540477034</v>
+      </c>
+      <c r="C13" t="n">
+        <v>484754.6953615946</v>
+      </c>
+      <c r="D13" t="n">
+        <v>585106.2003847008</v>
+      </c>
+      <c r="E13" t="n">
+        <v>692461.6183803611</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>369648.7749239895</v>
+      </c>
+      <c r="B14" t="n">
+        <v>438931.2422436419</v>
+      </c>
+      <c r="C14" t="n">
+        <v>533192.8260782126</v>
+      </c>
+      <c r="D14" t="n">
+        <v>649710.5400303868</v>
+      </c>
+      <c r="E14" t="n">
+        <v>773496.4385566801</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>400537.7074142257</v>
+      </c>
+      <c r="B15" t="n">
+        <v>478220.444301274</v>
+      </c>
+      <c r="C15" t="n">
+        <v>585834.168135072</v>
+      </c>
+      <c r="D15" t="n">
+        <v>719138.0565255021</v>
+      </c>
+      <c r="E15" t="n">
+        <v>865265.749852504</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>417357.0928401357</v>
+      </c>
+      <c r="B16" t="n">
+        <v>507507.0182938736</v>
+      </c>
+      <c r="C16" t="n">
+        <v>628629.1084490581</v>
+      </c>
+      <c r="D16" t="n">
+        <v>779861.00180054</v>
+      </c>
+      <c r="E16" t="n">
+        <v>947364.581609864</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>440075.8378572149</v>
+      </c>
+      <c r="B17" t="n">
+        <v>537423.1228064848</v>
+      </c>
+      <c r="C17" t="n">
+        <v>673390.8569420783</v>
+      </c>
+      <c r="D17" t="n">
+        <v>848356.1181168079</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1034374.71586807</v>
+      </c>
+      <c r="F17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>447387.1344489602</v>
+      </c>
+      <c r="B18" t="n">
+        <v>556516.7327356425</v>
+      </c>
+      <c r="C18" t="n">
+        <v>710012.8314252895</v>
+      </c>
+      <c r="D18" t="n">
+        <v>904485.1173033048</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1121897.004993387</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>455729.3224642329</v>
+      </c>
+      <c r="B19" t="n">
+        <v>577855.6597169689</v>
+      </c>
+      <c r="C19" t="n">
+        <v>748600.2589248751</v>
+      </c>
+      <c r="D19" t="n">
+        <v>963966.3093669356</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1210182.557492202</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>466747.7096879188</v>
+      </c>
+      <c r="B20" t="n">
+        <v>601157.5249200427</v>
+      </c>
+      <c r="C20" t="n">
+        <v>788298.3313434868</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1033184.963518028</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1304652.037527476</v>
+      </c>
+      <c r="F20" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>492621.8989371788</v>
+      </c>
+      <c r="B21" t="n">
+        <v>641066.2067744951</v>
+      </c>
+      <c r="C21" t="n">
+        <v>846487.6448663408</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1116586.951260546</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1431851.241432854</v>
+      </c>
+      <c r="F21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>519460.4255044904</v>
+      </c>
+      <c r="B22" t="n">
+        <v>679894.0092888556</v>
+      </c>
+      <c r="C22" t="n">
+        <v>905902.1355178005</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1211676.085084609</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1568199.03330314</v>
+      </c>
+      <c r="F22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>552999.6642074435</v>
+      </c>
+      <c r="B23" t="n">
+        <v>726105.8087880882</v>
+      </c>
+      <c r="C23" t="n">
+        <v>976368.2061785125</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1316154.300247669</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1720575.669043288</v>
+      </c>
+      <c r="F23" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>587764.8493924503</v>
+      </c>
+      <c r="B24" t="n">
+        <v>778419.7816989853</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1054109.793348694</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1429263.130083642</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1875782.796299756</v>
+      </c>
+      <c r="F24" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>624176.920531888</v>
+      </c>
+      <c r="B25" t="n">
+        <v>836745.750516552</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1136752.482478598</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1554786.935818375</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2046376.813726819</v>
+      </c>
+      <c r="F25" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>664167.4638758769</v>
+      </c>
+      <c r="B26" t="n">
+        <v>892044.7769446577</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1224409.891552228</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1679184.113114828</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2225430.331621269</v>
+      </c>
+      <c r="F26" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>707660.2760514553</v>
+      </c>
+      <c r="B27" t="n">
+        <v>961391.9074913844</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1320710.070178245</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1827172.568253553</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2423866.063554092</v>
+      </c>
+      <c r="F27" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>255670.9848559589</v>
+      </c>
+      <c r="B28" t="n">
+        <v>523590.3931820241</v>
+      </c>
+      <c r="C28" t="n">
+        <v>912158.1231031795</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1468759.2576856</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2127025.47189872</v>
+      </c>
+      <c r="F28" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>272440.7114861287</v>
+      </c>
+      <c r="B29" t="n">
+        <v>559107.561565789</v>
+      </c>
+      <c r="C29" t="n">
+        <v>982174.0924294845</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1587614.464996669</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2314336.427245236</v>
+      </c>
+      <c r="F29" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>290273.0602427588</v>
+      </c>
+      <c r="B30" t="n">
+        <v>596553.3205468782</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1055483.069819591</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1718131.228453763</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2508219.011972883</v>
+      </c>
+      <c r="F30" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>308912.1174782793</v>
+      </c>
+      <c r="B31" t="n">
+        <v>640756.8862819226</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1140301.48207127</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1855872.622261393</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2761555.366251208</v>
+      </c>
+      <c r="F31" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>333212.9903784204</v>
+      </c>
+      <c r="B32" t="n">
+        <v>688703.1540853103</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1224331.745361202</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2019278.42225861</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2999698.42570135</v>
+      </c>
+      <c r="F32" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>355265.8457745715</v>
+      </c>
+      <c r="B33" t="n">
+        <v>737503.2962711161</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1317746.031404275</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2181855.931864912</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3256825.108424844</v>
+      </c>
+      <c r="F33" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>380689.8277656937</v>
+      </c>
+      <c r="B34" t="n">
+        <v>788157.3056867088</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1422930.050341756</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2360410.53529432</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3553467.573872644</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>408799.1318890703</v>
+      </c>
+      <c r="B35" t="n">
+        <v>845468.3601149719</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1531764.363825772</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2547919.366632849</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3867853.368261833</v>
+      </c>
+      <c r="F35" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>438692.4475260337</v>
+      </c>
+      <c r="B36" t="n">
+        <v>904156.5613810641</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1649056.212047155</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2759067.789268943</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4223370.916928157</v>
+      </c>
+      <c r="F36" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>466480.007346219</v>
+      </c>
+      <c r="B37" t="n">
+        <v>973176.914389679</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1773413.152959759</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2993111.03986615</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4586987.72590914</v>
+      </c>
+      <c r="F37" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>503474.0879313131</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1041387.833513363</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1918066.122944931</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3238512.659854342</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5013503.609766653</v>
+      </c>
+      <c r="F38" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>536307.275694148</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1117828.739351017</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2066446.827250693</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3515074.81246604</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5445545.701611731</v>
+      </c>
+      <c r="F39" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>569410.7845699141</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1191501.582779806</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2220185.697328453</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3797859.504405804</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5875463.255745386</v>
+      </c>
+      <c r="F40" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>615584.3065259026</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1290069.963247137</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2382688.564175752</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4104778.516752</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6470027.680903153</v>
+      </c>
+      <c r="F41" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>654732.7077510436</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1387152.401959817</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2580933.266235474</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4431469.418379374</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6992865.832674773</v>
+      </c>
+      <c r="F42" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>702719.4342328539</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1484050.236817097</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2777344.327436646</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4824483.728760692</v>
+      </c>
+      <c r="E43" t="n">
+        <v>7616960.196385242</v>
+      </c>
+      <c r="F43" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>750163.3298773105</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1593743.320595261</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2993700.371465933</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5195361.052802132</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8259579.594608455</v>
+      </c>
+      <c r="F44" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>801827.0200714363</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1712654.304875634</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3221770.721945024</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5621321.070734562</v>
+      </c>
+      <c r="E45" t="n">
+        <v>8983064.201986175</v>
+      </c>
+      <c r="F45" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>857074.6980723598</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1835896.419347555</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3477877.012609647</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6084626.441870019</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9758452.657136636</v>
+      </c>
+      <c r="F46" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>915506.2276541966</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1964099.960523444</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3731155.86501677</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6580027.483958626</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10649229.56802876</v>
+      </c>
+      <c r="F47" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>984762.3651769029</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2109113.072933702</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4024098.844691321</v>
+      </c>
+      <c r="D48" t="n">
+        <v>7117968.958958141</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11515278.71328638</v>
+      </c>
+      <c r="F48" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1058211.445026823</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2268077.929896512</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4333332.16563703</v>
+      </c>
+      <c r="D49" t="n">
+        <v>7710417.780211817</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12474746.69651815</v>
+      </c>
+      <c r="F49" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1141060.436490231</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2439413.899661635</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4675868.094419305</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8344285.538826464</v>
+      </c>
+      <c r="E50" t="n">
+        <v>13522403.05906168</v>
+      </c>
+      <c r="F50" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1218444.402740445</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2622355.749903151</v>
+      </c>
+      <c r="C51" t="n">
+        <v>5035875.63883497</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8954018.433473721</v>
+      </c>
+      <c r="E51" t="n">
+        <v>14639432.6103281</v>
+      </c>
+      <c r="F51" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1311231.820282367</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2802980.66423178</v>
+      </c>
+      <c r="C52" t="n">
+        <v>5448079.025805857</v>
+      </c>
+      <c r="D52" t="n">
+        <v>9698456.44921816</v>
+      </c>
+      <c r="E52" t="n">
+        <v>15889098.76650925</v>
+      </c>
+      <c r="F52" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="B2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>144000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132358.1173465014</v>
+      </c>
+      <c r="B3" t="n">
+        <v>141172.3311191642</v>
+      </c>
+      <c r="C3" t="n">
+        <v>151010.8647201569</v>
+      </c>
+      <c r="D3" t="n">
+        <v>161267.0965038424</v>
+      </c>
+      <c r="E3" t="n">
+        <v>170682.9177969237</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>141174.8368799096</v>
+      </c>
+      <c r="B4" t="n">
+        <v>153419.9259013601</v>
+      </c>
+      <c r="C4" t="n">
+        <v>168400.3097013909</v>
+      </c>
+      <c r="D4" t="n">
+        <v>184028.1179575948</v>
+      </c>
+      <c r="E4" t="n">
+        <v>199439.3961008481</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>151892.0787747427</v>
+      </c>
+      <c r="B5" t="n">
+        <v>167218.0832245308</v>
+      </c>
+      <c r="C5" t="n">
+        <v>186587.892642363</v>
+      </c>
+      <c r="D5" t="n">
+        <v>207352.4414348647</v>
+      </c>
+      <c r="E5" t="n">
+        <v>227758.402352147</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>163351.468145487</v>
+      </c>
+      <c r="B6" t="n">
+        <v>182170.0774599322</v>
+      </c>
+      <c r="C6" t="n">
+        <v>205625.5463196979</v>
+      </c>
+      <c r="D6" t="n">
+        <v>231214.4907756061</v>
+      </c>
+      <c r="E6" t="n">
+        <v>257322.159004283</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>174596.6860125276</v>
+      </c>
+      <c r="B7" t="n">
+        <v>197110.7939690222</v>
+      </c>
+      <c r="C7" t="n">
+        <v>225379.4435360543</v>
+      </c>
+      <c r="D7" t="n">
+        <v>257295.2639870977</v>
+      </c>
+      <c r="E7" t="n">
+        <v>288881.5211313089</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>187317.9810934354</v>
+      </c>
+      <c r="B8" t="n">
+        <v>212969.1966738379</v>
+      </c>
+      <c r="C8" t="n">
+        <v>246144.1572326938</v>
+      </c>
+      <c r="D8" t="n">
+        <v>283212.5400068064</v>
+      </c>
+      <c r="E8" t="n">
+        <v>321686.1593829523</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>200472.081830319</v>
+      </c>
+      <c r="B9" t="n">
+        <v>229624.7873147884</v>
+      </c>
+      <c r="C9" t="n">
+        <v>267949.3326890952</v>
+      </c>
+      <c r="D9" t="n">
+        <v>311586.4155358124</v>
+      </c>
+      <c r="E9" t="n">
+        <v>357578.1543642246</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>213961.4946761923</v>
+      </c>
+      <c r="B10" t="n">
+        <v>247479.6677578273</v>
+      </c>
+      <c r="C10" t="n">
+        <v>290450.5766937857</v>
+      </c>
+      <c r="D10" t="n">
+        <v>340715.6747365507</v>
+      </c>
+      <c r="E10" t="n">
+        <v>394001.1988336552</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>228074.1946171195</v>
+      </c>
+      <c r="B11" t="n">
+        <v>265266.9205987204</v>
+      </c>
+      <c r="C11" t="n">
+        <v>314147.8651645432</v>
+      </c>
+      <c r="D11" t="n">
+        <v>371944.8608642945</v>
+      </c>
+      <c r="E11" t="n">
+        <v>432463.6215704507</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>242887.8695240552</v>
+      </c>
+      <c r="B12" t="n">
+        <v>284283.099727041</v>
+      </c>
+      <c r="C12" t="n">
+        <v>338588.9196972309</v>
+      </c>
+      <c r="D12" t="n">
+        <v>403122.3304790499</v>
+      </c>
+      <c r="E12" t="n">
+        <v>474047.2828937038</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>258920.9960379448</v>
+      </c>
+      <c r="B13" t="n">
+        <v>304948.5073260505</v>
+      </c>
+      <c r="C13" t="n">
+        <v>365376.0016676137</v>
+      </c>
+      <c r="D13" t="n">
+        <v>438260.8377906708</v>
+      </c>
+      <c r="E13" t="n">
+        <v>516979.2960596205</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>275402.7257567547</v>
+      </c>
+      <c r="B14" t="n">
+        <v>325210.1353470562</v>
+      </c>
+      <c r="C14" t="n">
+        <v>392365.9042733752</v>
+      </c>
+      <c r="D14" t="n">
+        <v>475179.3973235725</v>
+      </c>
+      <c r="E14" t="n">
+        <v>563101.2573563977</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>291860.418564107</v>
+      </c>
+      <c r="B15" t="n">
+        <v>345960.6973468186</v>
+      </c>
+      <c r="C15" t="n">
+        <v>420953.8156783793</v>
+      </c>
+      <c r="D15" t="n">
+        <v>513261.6356477648</v>
+      </c>
+      <c r="E15" t="n">
+        <v>613340.5496304431</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>293358.0121816668</v>
+      </c>
+      <c r="B16" t="n">
+        <v>354559.9482878059</v>
+      </c>
+      <c r="C16" t="n">
+        <v>436784.4982638934</v>
+      </c>
+      <c r="D16" t="n">
+        <v>538696.0973791513</v>
+      </c>
+      <c r="E16" t="n">
+        <v>650937.4816419517</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>297925.1477922304</v>
+      </c>
+      <c r="B17" t="n">
+        <v>362728.6532404171</v>
+      </c>
+      <c r="C17" t="n">
+        <v>452302.1351769639</v>
+      </c>
+      <c r="D17" t="n">
+        <v>566616.7408895961</v>
+      </c>
+      <c r="E17" t="n">
+        <v>688342.0957579614</v>
+      </c>
+      <c r="F17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>287621.1357098138</v>
+      </c>
+      <c r="B18" t="n">
+        <v>357861.0807907289</v>
+      </c>
+      <c r="C18" t="n">
+        <v>455899.6021537756</v>
+      </c>
+      <c r="D18" t="n">
+        <v>580188.660696458</v>
+      </c>
+      <c r="E18" t="n">
+        <v>717726.1324747432</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>277177.0752571572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>353125.6934190295</v>
+      </c>
+      <c r="C19" t="n">
+        <v>459486.0703077912</v>
+      </c>
+      <c r="D19" t="n">
+        <v>592745.223647448</v>
+      </c>
+      <c r="E19" t="n">
+        <v>743042.1632988978</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>267592.7657017076</v>
+      </c>
+      <c r="B20" t="n">
+        <v>349022.6469777534</v>
+      </c>
+      <c r="C20" t="n">
+        <v>461018.1561497097</v>
+      </c>
+      <c r="D20" t="n">
+        <v>608368.2877677679</v>
+      </c>
+      <c r="E20" t="n">
+        <v>771535.7980326648</v>
+      </c>
+      <c r="F20" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>272075.5043815093</v>
+      </c>
+      <c r="B21" t="n">
+        <v>358569.5991294689</v>
+      </c>
+      <c r="C21" t="n">
+        <v>478571.3022060455</v>
+      </c>
+      <c r="D21" t="n">
+        <v>635768.9755728182</v>
+      </c>
+      <c r="E21" t="n">
+        <v>818065.5003774191</v>
+      </c>
+      <c r="F21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>275866.7544755834</v>
+      </c>
+      <c r="B22" t="n">
+        <v>367062.422077471</v>
+      </c>
+      <c r="C22" t="n">
+        <v>495019.1218320272</v>
+      </c>
+      <c r="D22" t="n">
+        <v>667227.1702919058</v>
+      </c>
+      <c r="E22" t="n">
+        <v>865316.8058039774</v>
+      </c>
+      <c r="F22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>285161.7303325968</v>
+      </c>
+      <c r="B23" t="n">
+        <v>380072.4122577549</v>
+      </c>
+      <c r="C23" t="n">
+        <v>517521.6835157596</v>
+      </c>
+      <c r="D23" t="n">
+        <v>702355.1596891826</v>
+      </c>
+      <c r="E23" t="n">
+        <v>921863.7280852485</v>
+      </c>
+      <c r="F23" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>294657.5360452936</v>
+      </c>
+      <c r="B24" t="n">
+        <v>394963.2374997063</v>
+      </c>
+      <c r="C24" t="n">
+        <v>541503.7307041672</v>
+      </c>
+      <c r="D24" t="n">
+        <v>739038.3426684747</v>
+      </c>
+      <c r="E24" t="n">
+        <v>975357.5728623336</v>
+      </c>
+      <c r="F24" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>303546.8117053696</v>
+      </c>
+      <c r="B25" t="n">
+        <v>412355.1073702953</v>
+      </c>
+      <c r="C25" t="n">
+        <v>565893.7043165803</v>
+      </c>
+      <c r="D25" t="n">
+        <v>779434.0352418484</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1030060.964281491</v>
+      </c>
+      <c r="F25" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>313860.3985140814</v>
+      </c>
+      <c r="B26" t="n">
+        <v>426887.1266000959</v>
+      </c>
+      <c r="C26" t="n">
+        <v>591025.4613461688</v>
+      </c>
+      <c r="D26" t="n">
+        <v>815825.8943389941</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1087650.948499074</v>
+      </c>
+      <c r="F26" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>324301.0310000495</v>
+      </c>
+      <c r="B27" t="n">
+        <v>445602.9957390968</v>
+      </c>
+      <c r="C27" t="n">
+        <v>617754.266084807</v>
+      </c>
+      <c r="D27" t="n">
+        <v>861035.6000018133</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1148464.697207463</v>
+      </c>
+      <c r="F27" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>153286.3631192521</v>
+      </c>
+      <c r="D28" t="n">
+        <v>409623.9955141621</v>
+      </c>
+      <c r="E28" t="n">
+        <v>717887.4681093362</v>
+      </c>
+      <c r="F28" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>159008.57522111</v>
+      </c>
+      <c r="D29" t="n">
+        <v>426188.9391457625</v>
+      </c>
+      <c r="E29" t="n">
+        <v>748570.2207656909</v>
+      </c>
+      <c r="F29" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>164396.5620781152</v>
+      </c>
+      <c r="D30" t="n">
+        <v>445146.0160144855</v>
+      </c>
+      <c r="E30" t="n">
+        <v>786425.2092011557</v>
+      </c>
+      <c r="F30" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>172313.4619658666</v>
+      </c>
+      <c r="D31" t="n">
+        <v>464654.9223996194</v>
+      </c>
+      <c r="E31" t="n">
+        <v>829601.461165678</v>
+      </c>
+      <c r="F31" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>180058.1502279092</v>
+      </c>
+      <c r="D32" t="n">
+        <v>490053.718248729</v>
+      </c>
+      <c r="E32" t="n">
+        <v>879270.4017871744</v>
+      </c>
+      <c r="F32" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>188158.2613176513</v>
+      </c>
+      <c r="D33" t="n">
+        <v>515119.7132841792</v>
+      </c>
+      <c r="E33" t="n">
+        <v>924330.9865855103</v>
+      </c>
+      <c r="F33" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>196588.1718983255</v>
+      </c>
+      <c r="D34" t="n">
+        <v>536321.5836451945</v>
+      </c>
+      <c r="E34" t="n">
+        <v>975456.0370221494</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>204152.6995220752</v>
+      </c>
+      <c r="D35" t="n">
+        <v>561023.9654660071</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1014123.056282845</v>
+      </c>
+      <c r="F35" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>212807.4237549869</v>
+      </c>
+      <c r="D36" t="n">
+        <v>586784.5528852714</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1070527.870974534</v>
+      </c>
+      <c r="F36" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>220605.1599468002</v>
+      </c>
+      <c r="D37" t="n">
+        <v>613206.0670913237</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1126573.534523322</v>
+      </c>
+      <c r="F37" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>230251.9088631201</v>
+      </c>
+      <c r="D38" t="n">
+        <v>645558.5527860862</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1190450.159143731</v>
+      </c>
+      <c r="F38" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>239603.4355525717</v>
+      </c>
+      <c r="D39" t="n">
+        <v>676561.6653554246</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1255466.357932514</v>
+      </c>
+      <c r="F39" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>251367.8437608126</v>
+      </c>
+      <c r="D40" t="n">
+        <v>707700.0544908177</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1321750.638917235</v>
+      </c>
+      <c r="F40" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>262542.1632363425</v>
+      </c>
+      <c r="D41" t="n">
+        <v>741781.9571310893</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1386251.649922325</v>
+      </c>
+      <c r="F41" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>274534.0743478951</v>
+      </c>
+      <c r="D42" t="n">
+        <v>771874.8154256151</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1464076.351041272</v>
+      </c>
+      <c r="F42" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>286998.317482679</v>
+      </c>
+      <c r="D43" t="n">
+        <v>809714.2587611997</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1528996.002122362</v>
+      </c>
+      <c r="F43" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>298546.3354477088</v>
+      </c>
+      <c r="D44" t="n">
+        <v>843744.9873329554</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1611760.22036105</v>
+      </c>
+      <c r="F44" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>312879.4893957092</v>
+      </c>
+      <c r="D45" t="n">
+        <v>881224.3040963637</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1695180.656373233</v>
+      </c>
+      <c r="F45" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>326256.4637445419</v>
+      </c>
+      <c r="D46" t="n">
+        <v>920197.5194500866</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1785805.186109843</v>
+      </c>
+      <c r="F46" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>340253.551452314</v>
+      </c>
+      <c r="D47" t="n">
+        <v>966062.142029818</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1871955.388266407</v>
+      </c>
+      <c r="F47" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>352449.6162720873</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1009475.392205246</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1973142.417860637</v>
+      </c>
+      <c r="F48" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>367726.2377355087</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1062539.115542519</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2067611.388542252</v>
+      </c>
+      <c r="F49" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>382112.9155767026</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1111874.722447516</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2167146.942242452</v>
+      </c>
+      <c r="F50" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>400072.030485756</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1158486.413944499</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2275507.044724835</v>
+      </c>
+      <c r="F51" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>414317.8806113914</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1208594.897917751</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2387510.6395635</v>
+      </c>
+      <c r="F52" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/nexum_proyecto_final/resultados/resultados_modelo.xlsx
+++ b/nexum_proyecto_final/resultados/resultados_modelo.xlsx
@@ -5884,13 +5884,13 @@
         <v>0.6374582321489426</v>
       </c>
       <c r="G2" t="n">
-        <v>0.646056357936119</v>
+        <v>0.6460563579361195</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1227421121469743</v>
+        <v>0.1227421121469742</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.00567473607935846</v>
+        <v>-0.005674736079358512</v>
       </c>
       <c r="J2" t="n">
         <v>-0.2047527980997257</v>
@@ -5908,10 +5908,10 @@
         <v>128</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02017415013410974</v>
+        <v>0.02062994851390809</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1837265751457567</v>
+        <v>0.2713880638250771</v>
       </c>
     </row>
     <row r="3">
@@ -5926,37 +5926,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09461853044171575</v>
+        <v>0.09267204755497915</v>
       </c>
       <c r="D3" t="n">
-        <v>0.109563056609669</v>
+        <v>0.1086374276463029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6899387144496072</v>
+        <v>0.6783997168545667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5946386979890954</v>
+        <v>0.575277632619389</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6791364818698665</v>
+        <v>0.6764060351347934</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1113057484709373</v>
+        <v>0.108957632437998</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01373215226361699</v>
+        <v>-0.01526522243585199</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2139947803662722</v>
+        <v>-0.2032541931862171</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4421534500970876</v>
+        <v>0.4559416270938875</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04410011138505539</v>
+        <v>0.04460239812706181</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06496579281159565</v>
+        <v>0.06504077521155971</v>
       </c>
       <c r="N3" t="n">
         <v>128</v>
@@ -6014,10 +6014,10 @@
         <v>128</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04164890770488457</v>
+        <v>0.04101089576373262</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7517799929394864</v>
+        <v>0.809614352365897</v>
       </c>
     </row>
     <row r="5">
@@ -6047,10 +6047,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1315257670242158</v>
+        <v>0.1315257670242157</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-6.245004513516506e-17</v>
       </c>
       <c r="J5" t="n">
         <v>-0.2392718402314563</v>
@@ -6068,10 +6068,10 @@
         <v>128</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06201548897921966</v>
+        <v>0.06138645454050078</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9019355247608168</v>
+        <v>0.9420020638429865</v>
       </c>
     </row>
     <row r="6">
@@ -6098,13 +6098,13 @@
         <v>0.7459041975308476</v>
       </c>
       <c r="G6" t="n">
-        <v>0.636068137261486</v>
+        <v>0.6360681372614863</v>
       </c>
       <c r="H6" t="n">
         <v>0.1324344330844558</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.001551231754678199</v>
+        <v>-0.00155123175467823</v>
       </c>
       <c r="J6" t="n">
         <v>-0.2047527980997259</v>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02017415013410974</v>
+        <v>0.02062994851390809</v>
       </c>
     </row>
     <row r="3">
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02419747732560756</v>
+        <v>0.02483686049968294</v>
       </c>
     </row>
     <row r="4">
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1751620058559213</v>
+        <v>0.1962564546614131</v>
       </c>
     </row>
     <row r="12">
@@ -6496,7 +6496,7 @@
         <v>0.1362219757949842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005254302662653483</v>
+        <v>0.005254302662653504</v>
       </c>
       <c r="J2" t="n">
         <v>-0.3742419535852077</v>
@@ -6648,13 +6648,13 @@
         <v>0.7947274691867576</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5426249453251287</v>
+        <v>0.5426249453251291</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1714806773751311</v>
+        <v>0.171480677375131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0198641220271171</v>
+        <v>0.01986412202711706</v>
       </c>
       <c r="J5" t="n">
         <v>-0.178478223989074</v>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEZCLA_CMD</t>
+          <t>DJP</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6701,7 +6701,7 @@
         <v>0.16737434321456</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5863269572149877</v>
+        <v>0.5863269572149876</v>
       </c>
       <c r="I6" t="n">
         <v>0.07612205050138063</v>
@@ -6722,10 +6722,10 @@
         <v>128</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1751620058559213</v>
+        <v>0.1962564546614131</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.04007640397496848</v>
+        <v>0.1220288343904893</v>
       </c>
     </row>
     <row r="7">
@@ -6755,10 +6755,10 @@
         <v>0.1458954336728013</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5117313845944238</v>
+        <v>0.5117313845944237</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05498188602086723</v>
+        <v>0.05498188602086722</v>
       </c>
       <c r="J7" t="n">
         <v>-0.3143638938037138</v>

--- a/nexum_proyecto_final/resultados/resultados_modelo.xlsx
+++ b/nexum_proyecto_final/resultados/resultados_modelo.xlsx
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.045564080984627</v>
+        <v>0.04653130500365561</v>
       </c>
     </row>
     <row r="3">
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04930438691645928</v>
+        <v>0.05034109182863089</v>
       </c>
     </row>
     <row r="4">
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04934401368977564</v>
+        <v>0.05040198647251756</v>
       </c>
     </row>
     <row r="5">
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04980583351961895</v>
+        <v>0.05085108572178737</v>
       </c>
     </row>
     <row r="6">
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05369146964416108</v>
+        <v>0.0548303552432743</v>
       </c>
     </row>
     <row r="7">
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05622355851730596</v>
+        <v>0.05740907235642809</v>
       </c>
     </row>
     <row r="8">
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04061423840906504</v>
+        <v>0.04165024480575189</v>
       </c>
     </row>
     <row r="9">
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03921642310646538</v>
+        <v>0.04010861685587032</v>
       </c>
     </row>
     <row r="10">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03279627602421104</v>
+        <v>0.03375724729087864</v>
       </c>
     </row>
   </sheetData>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>299788.9134278799</v>
+        <v>293788.9134278799</v>
       </c>
     </row>
     <row r="4">
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6081147037452193</v>
+        <v>0.5959438459881693</v>
       </c>
     </row>
     <row r="6">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.045564080984627</v>
+        <v>0.04653130500365561</v>
       </c>
     </row>
     <row r="7">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2435085051757777</v>
+        <v>0.2459947939366955</v>
       </c>
     </row>
     <row r="8">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5608046279912542</v>
+        <v>0.5622851703539117</v>
       </c>
     </row>
     <row r="9">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1956868668329683</v>
+        <v>0.1917200357093929</v>
       </c>
     </row>
   </sheetData>
